--- a/Excel/PlayerLevelConfig.xlsx
+++ b/Excel/PlayerLevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Id</t>
   </si>
@@ -35,7 +35,13 @@
     <t>所需经验值</t>
   </si>
   <si>
+    <t>打造队列数量</t>
+  </si>
+  <si>
     <t>NeedExp</t>
+  </si>
+  <si>
+    <t>ForgeTheNumOfQueues</t>
   </si>
   <si>
     <t>int</t>
@@ -54,7 +60,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,19 +69,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -557,146 +550,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1047,281 +1038,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <dimension ref="C3:E35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="18.6166666666667" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2"/>
-    </row>
-    <row r="3" spans="3:4">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="3:5">
+      <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="3:4">
-      <c r="C4" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5">
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4">
-      <c r="C5" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="3:4">
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4">
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4">
-      <c r="C8" s="5">
+    <row r="5" spans="3:5">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5">
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4">
-      <c r="C9" s="5">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5">
+      <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4">
-      <c r="C10" s="5">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5">
+      <c r="C10" s="3">
         <v>5</v>
       </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4">
-      <c r="C11" s="5">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5">
+      <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4">
-      <c r="C12" s="5">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5">
+      <c r="C12" s="3">
         <v>7</v>
       </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4">
-      <c r="C13" s="5">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5">
+      <c r="C13" s="3">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4">
-      <c r="C14" s="5">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
+      <c r="C14" s="3">
         <v>9</v>
       </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:4">
-      <c r="C15" s="5">
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5">
+      <c r="C15" s="3">
         <v>10</v>
       </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="3:4">
-      <c r="C16" s="5">
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5">
+      <c r="C16" s="3">
         <v>11</v>
       </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4">
-      <c r="C17" s="5">
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" s="3">
         <v>12</v>
       </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="2"/>
-      <c r="C18" s="5">
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18" s="3">
         <v>13</v>
       </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4">
-      <c r="C19" s="5">
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4">
-      <c r="C20" s="5">
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="C20" s="3">
         <v>15</v>
       </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4">
-      <c r="C21" s="5">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="C21" s="3">
         <v>16</v>
       </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4">
-      <c r="C22" s="5">
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="C22" s="3">
         <v>17</v>
       </c>
-      <c r="D22" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4">
-      <c r="C23" s="5">
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="C23" s="3">
         <v>18</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4">
-      <c r="C24" s="5">
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24" s="3">
         <v>19</v>
       </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4">
-      <c r="C25" s="5">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5">
+      <c r="C25" s="3">
         <v>20</v>
       </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4">
-      <c r="C26" s="5">
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26" s="3">
         <v>21</v>
       </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4">
-      <c r="C27" s="5">
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5">
+      <c r="C27" s="3">
         <v>22</v>
       </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4">
-      <c r="C28" s="5">
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5">
+      <c r="C28" s="3">
         <v>23</v>
       </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4">
-      <c r="C29" s="5">
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29" s="3">
         <v>24</v>
       </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4">
-      <c r="C30" s="5">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5">
+      <c r="C30" s="3">
         <v>25</v>
       </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4">
-      <c r="C31" s="5">
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5">
+      <c r="C31" s="3">
         <v>26</v>
       </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" s="5">
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5">
+      <c r="C32" s="3">
         <v>27</v>
       </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33" s="5">
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5">
+      <c r="C33" s="3">
         <v>28</v>
       </c>
-      <c r="D33" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4">
-      <c r="C34" s="5">
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="C34" s="3">
         <v>29</v>
       </c>
-      <c r="D34" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4">
-      <c r="C35" s="5">
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5">
+      <c r="C35" s="3">
         <v>30</v>
       </c>
-      <c r="D35" s="6">
-        <v>1</v>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
